--- a/notebooks/test_output/shap_per_class_20hz_no_load.xlsx
+++ b/notebooks/test_output/shap_per_class_20hz_no_load.xlsx
@@ -496,16 +496,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.08947038215280392</v>
+        <v>0.0892521967843936</v>
       </c>
       <c r="E2" t="n">
-        <v>17.60060811429969</v>
+        <v>22.26644576250819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01119368457959839</v>
+        <v>0.0114020215927013</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
         <v>2</v>
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1335743092130243</v>
+        <v>0.1207519052953107</v>
       </c>
       <c r="E3" t="n">
-        <v>10.70360982013237</v>
+        <v>13.62664166459449</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01302437585798219</v>
+        <v>0.01251179927187388</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -558,20 +558,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_correlation</t>
+          <t>current_phase_a_rms</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.09205584583735392</v>
+        <v>0.0823856130692415</v>
       </c>
       <c r="E4" t="n">
-        <v>6.567371294726433</v>
+        <v>37.8283950509337</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0114119922608798</v>
+        <v>0.01118256471075033</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08947038215280392</v>
+        <v>0.0892521967843936</v>
       </c>
       <c r="C2" t="n">
-        <v>0.005083358800201473</v>
+        <v>0.004008361957354538</v>
       </c>
       <c r="D2" t="n">
-        <v>17.60060811429969</v>
+        <v>22.26644576250819</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0598043314413836</v>
+        <v>0.05349509833719766</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003965517981583669</v>
+        <v>0.003637456486392708</v>
       </c>
       <c r="D3" t="n">
-        <v>15.08105143101278</v>
+        <v>14.70669174199018</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -677,17 +677,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_env_thd_power_frac</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01934626971777358</v>
+        <v>0.02075476983887545</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005117110359299441</v>
+        <v>0.003388256910477684</v>
       </c>
       <c r="D4" t="n">
-        <v>3.780694679697192</v>
+        <v>6.125482551181132</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -701,17 +701,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>current_phase_a_env_thd_power_frac</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01785408286752348</v>
+        <v>0.01635894896459728</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002003337538673498</v>
+        <v>0.00338062203455636</v>
       </c>
       <c r="D5" t="n">
-        <v>8.912124592892868</v>
+        <v>4.839020868695063</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -725,17 +725,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_env_fundamental_power_ratio</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01737711080385931</v>
+        <v>0.01448599006623655</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003500129330335388</v>
+        <v>0.00342001771375219</v>
       </c>
       <c r="D6" t="n">
-        <v>4.964691163364121</v>
+        <v>4.235635286809897</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -749,17 +749,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01119049018831471</v>
+        <v>0.01435504162927167</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001634222966783054</v>
+        <v>0.002683987220386127</v>
       </c>
       <c r="D7" t="n">
-        <v>6.847548920973551</v>
+        <v>5.348381704809112</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -773,17 +773,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>current_phase_a_env_ptp</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009996664125381945</v>
+        <v>0.01321828918069374</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001506893360535688</v>
+        <v>0.002954038874866728</v>
       </c>
       <c r="D8" t="n">
-        <v>6.633911893214066</v>
+        <v>4.474634557727176</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -797,17 +797,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>current_phase_a_env_fundamental_power_ratio</t>
+          <t>current_phase_a_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009145379591010005</v>
+        <v>0.01273307814445003</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001887251195291373</v>
+        <v>0.001325689235362773</v>
       </c>
       <c r="D9" t="n">
-        <v>4.845847312405561</v>
+        <v>9.604801605671637</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -821,17 +821,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_env_peak_freq_cv</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.008630382388641101</v>
+        <v>0.009375271019915376</v>
       </c>
       <c r="C10" t="n">
-        <v>0.002914212626336436</v>
+        <v>0.002285166053528553</v>
       </c>
       <c r="D10" t="n">
-        <v>2.961469830975349</v>
+        <v>4.102647148537622</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -845,17 +845,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>current_phase_a_env_skew</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.008334877817544778</v>
+        <v>0.008527769695530976</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001769702756283999</v>
+        <v>0.00346929531284653</v>
       </c>
       <c r="D11" t="n">
-        <v>4.709734835751626</v>
+        <v>2.458062616730041</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -869,17 +869,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_mean</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.007157449673629128</v>
+        <v>0.007979525085010387</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00208556742788595</v>
+        <v>0.0009550418300052336</v>
       </c>
       <c r="D12" t="n">
-        <v>3.43187914192392</v>
+        <v>8.355070200710111</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -893,17 +893,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.007104264198398573</v>
+        <v>0.007849237663050197</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002194874394543194</v>
+        <v>0.00141470211112165</v>
       </c>
       <c r="D13" t="n">
-        <v>3.236737304279361</v>
+        <v>5.548293254397145</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -917,17 +917,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_env_peak_power_std</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.006354681821574208</v>
+        <v>0.007691985392600087</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001253286656350524</v>
+        <v>0.00182410936543081</v>
       </c>
       <c r="D14" t="n">
-        <v>5.070373234760245</v>
+        <v>4.216821299292242</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -941,17 +941,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_time_corr</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.006336957435771789</v>
+        <v>0.007075366517356023</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001193097037751115</v>
+        <v>0.001335475946214278</v>
       </c>
       <c r="D15" t="n">
-        <v>5.311306727111681</v>
+        <v>5.297971526703571</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -965,17 +965,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>current_phase_a_env_form_factor</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.006115930160840832</v>
+        <v>0.006926927307726595</v>
       </c>
       <c r="C16" t="n">
-        <v>0.001938746113071593</v>
+        <v>0.002256605423040095</v>
       </c>
       <c r="D16" t="n">
-        <v>3.154563959646939</v>
+        <v>3.069609131003232</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -989,17 +989,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_std</t>
+          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.006048303256463411</v>
+        <v>0.006350715936944357</v>
       </c>
       <c r="C17" t="n">
-        <v>0.002022824028151887</v>
+        <v>0.002179243110606735</v>
       </c>
       <c r="D17" t="n">
-        <v>2.990014589575249</v>
+        <v>2.914170871678246</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
@@ -1013,17 +1013,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>current_phase_a_env_entropy</t>
+          <t>current_phase_a_env_spread</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.00589560173599492</v>
+        <v>0.00596851045469447</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0009997074828225212</v>
+        <v>0.001864850319006164</v>
       </c>
       <c r="D18" t="n">
-        <v>5.897267815452978</v>
+        <v>3.200513407822016</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1037,17 +1037,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>current_phase_a_form_factor</t>
+          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.005445830249082585</v>
+        <v>0.005546382027397544</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001228360529527491</v>
+        <v>0.001744925355672819</v>
       </c>
       <c r="D19" t="n">
-        <v>4.433377485193652</v>
+        <v>3.17856017380022</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -1061,17 +1061,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>current_phase_a_env_spread</t>
+          <t>current_phase_a_env_peak_power_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005362686608860113</v>
+        <v>0.005530457793740922</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00144494788316107</v>
+        <v>0.002158733998026114</v>
       </c>
       <c r="D20" t="n">
-        <v>3.711309977511873</v>
+        <v>2.561886818815846</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -1085,17 +1085,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>current_phase_a_env_dom_rel_peak_power</t>
+          <t>current_phase_a_env_form_factor</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.005251352450626504</v>
+        <v>0.005471134990224325</v>
       </c>
       <c r="C21" t="n">
-        <v>0.001671036718280791</v>
+        <v>0.0007075737873037855</v>
       </c>
       <c r="D21" t="n">
-        <v>3.142552744443439</v>
+        <v>7.732137293693268</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -1109,17 +1109,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
+          <t>current_phase_a_form_factor</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.005059569858465314</v>
+        <v>0.005393046706631337</v>
       </c>
       <c r="C22" t="n">
-        <v>0.001571803907391841</v>
+        <v>0.001280486229529855</v>
       </c>
       <c r="D22" t="n">
-        <v>3.218936945825104</v>
+        <v>4.211684956394943</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -1133,17 +1133,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>current_phase_a_skewness</t>
+          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.004834556544988275</v>
+        <v>0.005273866514846195</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0009821143342240775</v>
+        <v>0.001476438694450667</v>
       </c>
       <c r="D23" t="n">
-        <v>4.922550410898629</v>
+        <v>3.571994431413961</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -1157,17 +1157,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
+          <t>current_phase_a_env_rms</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.004710187716018539</v>
+        <v>0.005063336554196192</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00101897298488716</v>
+        <v>0.00111330374692445</v>
       </c>
       <c r="D24" t="n">
-        <v>4.622440007219686</v>
+        <v>4.547987095447044</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -1181,17 +1181,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_freq_cv</t>
+          <t>current_phase_a_env_flatness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.004638591599508209</v>
+        <v>0.004808392246997235</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0009617067854271746</v>
+        <v>0.001059085121141718</v>
       </c>
       <c r="D25" t="n">
-        <v>4.823240760477985</v>
+        <v>4.540094795086705</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -1205,17 +1205,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_std</t>
+          <t>current_phase_a_env_peak_sp_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.004542299226515254</v>
+        <v>0.004431840687220879</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0007895852233602082</v>
+        <v>0.001804273529084105</v>
       </c>
       <c r="D26" t="n">
-        <v>5.752693395465345</v>
+        <v>2.456288391365287</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1229,17 +1229,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
+          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.004348276181978208</v>
+        <v>0.004360354051122903</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001453039602926541</v>
+        <v>0.001254559636054884</v>
       </c>
       <c r="D27" t="n">
-        <v>2.992517373956459</v>
+        <v>3.47557754134275</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1253,17 +1253,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_mean</t>
+          <t>current_phase_a_current_phase_b_env_crest_diff</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.00424774008812694</v>
+        <v>0.00415584943348344</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001502649213298345</v>
+        <v>0.0006879264185905461</v>
       </c>
       <c r="D28" t="n">
-        <v>2.826815322153535</v>
+        <v>6.041037109211347</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
@@ -1277,17 +1277,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
+          <t>current_phase_a_env_ptp</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.00409939927326536</v>
+        <v>0.004085609314207334</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001032961548902842</v>
+        <v>0.0009989348703754188</v>
       </c>
       <c r="D29" t="n">
-        <v>3.968550031817903</v>
+        <v>4.08992471493637</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -1301,17 +1301,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
+          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.003881633591173469</v>
+        <v>0.003753430244055544</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0009267794249326172</v>
+        <v>0.0007273005530633367</v>
       </c>
       <c r="D30" t="n">
-        <v>4.188258396944576</v>
+        <v>5.16069817527958</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -1325,17 +1325,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>current_phase_a_env_harmonic_ratio</t>
+          <t>current_phase_a_env_peak_sp_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.003390196541462896</v>
+        <v>0.00308145843795001</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0005814341905588063</v>
+        <v>0.00158910985149029</v>
       </c>
       <c r="D31" t="n">
-        <v>5.830648231612209</v>
+        <v>1.939097567159703</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002222427240167349</v>
+        <v>0.00151080994582323</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0008330136128205445</v>
+        <v>0.0007310159067710966</v>
       </c>
       <c r="D32" t="n">
-        <v>2.667904253809093</v>
+        <v>2.066698227558581</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1447,13 +1447,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1335743092130243</v>
+        <v>0.1207519052953107</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01247936018049603</v>
+        <v>0.008861447449861266</v>
       </c>
       <c r="D2" t="n">
-        <v>10.70360982013237</v>
+        <v>13.62664166459449</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
@@ -1471,13 +1471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06996646778779707</v>
+        <v>0.06981254261203576</v>
       </c>
       <c r="C3" t="n">
-        <v>0.009905552146559001</v>
+        <v>0.004737963465589383</v>
       </c>
       <c r="D3" t="n">
-        <v>7.063351554671943</v>
+        <v>14.7346841680447</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -1495,13 +1495,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02742571917860786</v>
+        <v>0.03380165670763714</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001494243597575974</v>
+        <v>0.004368471176364656</v>
       </c>
       <c r="D4" t="n">
-        <v>18.35412624945239</v>
+        <v>7.737622148979033</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
@@ -1515,17 +1515,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01905605451338522</v>
+        <v>0.01445695187077699</v>
       </c>
       <c r="C5" t="n">
-        <v>0.004208444717546862</v>
+        <v>0.001491310756378274</v>
       </c>
       <c r="D5" t="n">
-        <v>4.528040763735039</v>
+        <v>9.694059315506491</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
@@ -1543,13 +1543,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01723419891648958</v>
+        <v>0.01363966043589387</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004297733926195545</v>
+        <v>0.003691638748959012</v>
       </c>
       <c r="D6" t="n">
-        <v>4.010057186386547</v>
+        <v>3.694734077758629</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -1563,17 +1563,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01181756374615098</v>
+        <v>0.01351857518865348</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001615055837217617</v>
+        <v>0.003142131357462593</v>
       </c>
       <c r="D7" t="n">
-        <v>7.317078643995035</v>
+        <v>4.302344691319133</v>
       </c>
       <c r="E7" t="n">
         <v>2</v>
@@ -1587,17 +1587,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>current_phase_a_env_entropy</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01038047325630957</v>
+        <v>0.01007516981552319</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001356663559808088</v>
+        <v>0.00158876742748563</v>
       </c>
       <c r="D8" t="n">
-        <v>7.651415612299518</v>
+        <v>6.34146082467194</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
@@ -1611,17 +1611,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01025048204327239</v>
+        <v>0.009830499748656915</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004989974677409688</v>
+        <v>0.003228291489443207</v>
       </c>
       <c r="D9" t="n">
-        <v>2.054211126073726</v>
+        <v>3.045099654045139</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
@@ -1635,17 +1635,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.009899670235698496</v>
+        <v>0.008654555308650997</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003113364655548736</v>
+        <v>0.001171974388591395</v>
       </c>
       <c r="D10" t="n">
-        <v>3.179723396943266</v>
+        <v>7.384531221489123</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -1659,17 +1659,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_time_corr</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.008927770993022669</v>
+        <v>0.008648389374738821</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002699311693834165</v>
+        <v>0.001809274329392492</v>
       </c>
       <c r="D11" t="n">
-        <v>3.307412752402069</v>
+        <v>4.780005681938731</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
@@ -1683,17 +1683,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.008153133469123514</v>
+        <v>0.008391780740224305</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001764201659899393</v>
+        <v>0.001367115219078149</v>
       </c>
       <c r="D12" t="n">
-        <v>4.621403233208684</v>
+        <v>6.138267821496901</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1707,17 +1707,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>current_phase_a_env_ptp</t>
+          <t>current_phase_a_env_flatness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.007950204655173557</v>
+        <v>0.007240867880473423</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001790489010741917</v>
+        <v>0.002733114074963257</v>
       </c>
       <c r="D13" t="n">
-        <v>4.440217284386706</v>
+        <v>2.649300830065963</v>
       </c>
       <c r="E13" t="n">
         <v>2</v>
@@ -1731,17 +1731,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_phase_a_form_factor</t>
+          <t>current_phase_a_env_peak_freq_cv</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.007393227244433415</v>
+        <v>0.006773754587149681</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001440763860301628</v>
+        <v>0.001698681115792832</v>
       </c>
       <c r="D14" t="n">
-        <v>5.131427941707406</v>
+        <v>3.987631726671013</v>
       </c>
       <c r="E14" t="n">
         <v>2</v>
@@ -1755,17 +1755,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_phase_a_env_spread</t>
+          <t>current_phase_a_env_peak_power_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.007164237881727155</v>
+        <v>0.006479958665383178</v>
       </c>
       <c r="C15" t="n">
-        <v>0.001554979350547505</v>
+        <v>0.001781201048950779</v>
       </c>
       <c r="D15" t="n">
-        <v>4.607258486500024</v>
+        <v>3.637951083449765</v>
       </c>
       <c r="E15" t="n">
         <v>2</v>
@@ -1779,17 +1779,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_env_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.007062869558926904</v>
+        <v>0.006265130908933175</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00108344121025426</v>
+        <v>0.002832124800902284</v>
       </c>
       <c r="D16" t="n">
-        <v>6.518862586594389</v>
+        <v>2.212158442083046</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
@@ -1803,17 +1803,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>current_phase_a_env_skew</t>
+          <t>current_phase_a_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.006683225039643095</v>
+        <v>0.006123552815314355</v>
       </c>
       <c r="C17" t="n">
-        <v>0.002118040828920609</v>
+        <v>0.002220178502501499</v>
       </c>
       <c r="D17" t="n">
-        <v>3.155365748728971</v>
+        <v>2.758122928938202</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
@@ -1827,17 +1827,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_std</t>
+          <t>current_phase_a_form_factor</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.006458056982135013</v>
+        <v>0.005405674279797802</v>
       </c>
       <c r="C18" t="n">
-        <v>0.002995293284978106</v>
+        <v>0.001742711189394211</v>
       </c>
       <c r="D18" t="n">
-        <v>2.15606112894248</v>
+        <v>3.101858353875226</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -1851,17 +1851,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
+          <t>current_phase_a_env_ptp</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.005195182895393068</v>
+        <v>0.004871891433446982</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001077905988589623</v>
+        <v>0.001080722687908629</v>
       </c>
       <c r="D19" t="n">
-        <v>4.819654732267772</v>
+        <v>4.507952325264432</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -1879,13 +1879,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.004290261043976759</v>
+        <v>0.004561172933485074</v>
       </c>
       <c r="C20" t="n">
-        <v>0.001422228801676021</v>
+        <v>0.0008292315994949602</v>
       </c>
       <c r="D20" t="n">
-        <v>3.016554631276371</v>
+        <v>5.500415001204717</v>
       </c>
       <c r="E20" t="n">
         <v>2</v>
@@ -1899,17 +1899,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
+          <t>current_phase_a_env_spread</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.00394632276328411</v>
+        <v>0.004460549161624454</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008816813643284286</v>
+        <v>0.001279124216670156</v>
       </c>
       <c r="D21" t="n">
-        <v>4.475855070090162</v>
+        <v>3.487162725766309</v>
       </c>
       <c r="E21" t="n">
         <v>2</v>
@@ -1923,17 +1923,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>current_phase_a_env_dom_rel_peak_power</t>
+          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.003761132378917233</v>
+        <v>0.004357253284877782</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0009854598576372775</v>
+        <v>0.002752225205564586</v>
       </c>
       <c r="D22" t="n">
-        <v>3.816587945099377</v>
+        <v>1.583168937040011</v>
       </c>
       <c r="E22" t="n">
         <v>2</v>
@@ -1947,17 +1947,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
+          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.003753681503967562</v>
+        <v>0.004308614990325007</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001106932759870773</v>
+        <v>0.002048177603242645</v>
       </c>
       <c r="D23" t="n">
-        <v>3.391034875557408</v>
+        <v>2.103623214740536</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
@@ -1971,17 +1971,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_freq_cv</t>
+          <t>current_phase_a_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.003743044993270597</v>
+        <v>0.00402448561736194</v>
       </c>
       <c r="C24" t="n">
-        <v>0.002289194350967385</v>
+        <v>0.0004324865364449413</v>
       </c>
       <c r="D24" t="n">
-        <v>1.635085566602579</v>
+        <v>9.305243575919999</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -1995,17 +1995,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
+          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.003497057621920722</v>
+        <v>0.003790679890657642</v>
       </c>
       <c r="C25" t="n">
-        <v>0.000996103601392876</v>
+        <v>0.0007781429252747489</v>
       </c>
       <c r="D25" t="n">
-        <v>3.510701607759146</v>
+        <v>4.87138166231173</v>
       </c>
       <c r="E25" t="n">
         <v>2</v>
@@ -2019,17 +2019,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
+          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.00349516563862998</v>
+        <v>0.003663689361454731</v>
       </c>
       <c r="C26" t="n">
-        <v>0.001069771272370886</v>
+        <v>0.001275720343827514</v>
       </c>
       <c r="D26" t="n">
-        <v>3.267177813726234</v>
+        <v>2.871836810326809</v>
       </c>
       <c r="E26" t="n">
         <v>2</v>
@@ -2043,17 +2043,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>current_phase_a_skewness</t>
+          <t>current_phase_a_env_peak_power_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.003451071616451398</v>
+        <v>0.003596454229129025</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00138089732083769</v>
+        <v>0.001315993010440128</v>
       </c>
       <c r="D27" t="n">
-        <v>2.499133406257777</v>
+        <v>2.732861703656905</v>
       </c>
       <c r="E27" t="n">
         <v>2</v>
@@ -2067,17 +2067,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_mean</t>
+          <t>current_phase_a_env_peak_sp_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.003110465896265891</v>
+        <v>0.003492102502151986</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0005062990775791393</v>
+        <v>0.001803677835982707</v>
       </c>
       <c r="D28" t="n">
-        <v>6.14341325093012</v>
+        <v>1.936090288178595</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -2091,17 +2091,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_mean</t>
+          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002631362765628965</v>
+        <v>0.003083919279418024</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001127789289520197</v>
+        <v>0.000469742030327355</v>
       </c>
       <c r="D29" t="n">
-        <v>2.333183563848878</v>
+        <v>6.564994040087364</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
@@ -2115,17 +2115,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_std</t>
+          <t>current_phase_a_current_phase_b_env_crest_diff</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002624069130280448</v>
+        <v>0.003007787692226889</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0001635662370705581</v>
+        <v>0.0009303650629838605</v>
       </c>
       <c r="D30" t="n">
-        <v>16.04187244598715</v>
+        <v>3.232876516036916</v>
       </c>
       <c r="E30" t="n">
         <v>2</v>
@@ -2139,17 +2139,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>current_phase_a_env_harmonic_ratio</t>
+          <t>current_phase_a_env_peak_sp_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002365517306634709</v>
+        <v>0.00234930270648911</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0003173654083221564</v>
+        <v>0.001095141069562789</v>
       </c>
       <c r="D31" t="n">
-        <v>7.453373023260698</v>
+        <v>2.145185967290348</v>
       </c>
       <c r="E31" t="n">
         <v>2</v>
@@ -2167,13 +2167,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.001518027185887725</v>
+        <v>0.0009390473821616043</v>
       </c>
       <c r="C32" t="n">
-        <v>0.000933819344405253</v>
+        <v>0.0004622158737548597</v>
       </c>
       <c r="D32" t="n">
-        <v>1.625593792894292</v>
+        <v>2.031576844743281</v>
       </c>
       <c r="E32" t="n">
         <v>2</v>
@@ -2257,17 +2257,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_correlation</t>
+          <t>current_phase_a_rms</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09205584583735392</v>
+        <v>0.0823856130692415</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01401714263324221</v>
+        <v>0.002177867569437301</v>
       </c>
       <c r="D2" t="n">
-        <v>6.567371294726433</v>
+        <v>37.8283950509337</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -2281,17 +2281,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>current_phase_a_rms</t>
+          <t>current_phase_a_current_phase_b_correlation</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0810782023322784</v>
+        <v>0.07999199579479901</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0131565216606536</v>
+        <v>0.004066370358822997</v>
       </c>
       <c r="D3" t="n">
-        <v>6.162581782458199</v>
+        <v>19.67154784751923</v>
       </c>
       <c r="E3" t="n">
         <v>3</v>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01238945955074899</v>
+        <v>0.01744738626763532</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001903219293073832</v>
+        <v>0.003486317541083496</v>
       </c>
       <c r="D4" t="n">
-        <v>6.509704109660509</v>
+        <v>5.004517235409541</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -2329,17 +2329,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01226762620732598</v>
+        <v>0.01415767507146678</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002776827850427346</v>
+        <v>0.003809326789379116</v>
       </c>
       <c r="D5" t="n">
-        <v>4.417840316256865</v>
+        <v>3.716572163149254</v>
       </c>
       <c r="E5" t="n">
         <v>3</v>
@@ -2353,17 +2353,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>current_phase_a_env_fundamental_power_ratio</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01213723371225801</v>
+        <v>0.01256166296600987</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002129655634859482</v>
+        <v>0.001385053918971009</v>
       </c>
       <c r="D6" t="n">
-        <v>5.699126432614311</v>
+        <v>9.069374195627141</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -2377,17 +2377,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01178506510693582</v>
+        <v>0.01107588820576635</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005153776826509512</v>
+        <v>0.0008682377329730983</v>
       </c>
       <c r="D7" t="n">
-        <v>2.286680746343064</v>
+        <v>12.75659905018091</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
@@ -2401,17 +2401,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_env_fundamental_power_ratio</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01099190334441814</v>
+        <v>0.009635984059141432</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002738007829832694</v>
+        <v>0.001755795758989793</v>
       </c>
       <c r="D8" t="n">
-        <v>4.014547759570212</v>
+        <v>5.4880695144123</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
@@ -2425,17 +2425,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>current_phase_a_env_skew</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01090063583621146</v>
+        <v>0.009099656029478631</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002252791901997871</v>
+        <v>0.002147713850842523</v>
       </c>
       <c r="D9" t="n">
-        <v>4.838701452863814</v>
+        <v>4.236883631901261</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -2449,17 +2449,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_std</t>
+          <t>current_phase_a_env_spread</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.009925056130816201</v>
+        <v>0.008862603389878239</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004659485924508484</v>
+        <v>0.00307378307514011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.130070782680889</v>
+        <v>2.883279119065054</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -2473,17 +2473,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>current_phase_a_form_factor</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.007829784030783892</v>
+        <v>0.008622907730825621</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002193239529859956</v>
+        <v>0.001967799383131168</v>
       </c>
       <c r="D11" t="n">
-        <v>3.569946749872934</v>
+        <v>4.381983237169494</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -2497,17 +2497,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_env_flatness</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.007469038311777962</v>
+        <v>0.007577123906339136</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0007629565975446013</v>
+        <v>0.001848535095065135</v>
       </c>
       <c r="D12" t="n">
-        <v>9.789469599082073</v>
+        <v>4.098966222986381</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
@@ -2521,17 +2521,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.007355772010820912</v>
+        <v>0.00714738720381055</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0007189339418575967</v>
+        <v>0.002279230472864301</v>
       </c>
       <c r="D13" t="n">
-        <v>10.23135683126445</v>
+        <v>3.135863586534374</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -2545,17 +2545,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.007232456798526332</v>
+        <v>0.007123055482060048</v>
       </c>
       <c r="C14" t="n">
-        <v>0.001457615645914035</v>
+        <v>0.0003969225598876777</v>
       </c>
       <c r="D14" t="n">
-        <v>4.961806770346076</v>
+        <v>17.94525368257948</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -2569,17 +2569,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_phase_a_env_entropy</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.006878410690493131</v>
+        <v>0.006588009437970535</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0006362741681382009</v>
+        <v>0.001315459924734431</v>
       </c>
       <c r="D15" t="n">
-        <v>10.81028105825688</v>
+        <v>5.008103426842336</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
@@ -2593,17 +2593,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_mean</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.00687048318827094</v>
+        <v>0.006350653751881742</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002559438634194517</v>
+        <v>0.001425536768906066</v>
       </c>
       <c r="D16" t="n">
-        <v>2.684360645679903</v>
+        <v>4.454889794149019</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
@@ -2617,17 +2617,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_time_corr</t>
+          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.006267273554009012</v>
+        <v>0.006025920240197833</v>
       </c>
       <c r="C17" t="n">
-        <v>0.002022082254481477</v>
+        <v>0.001583048827926205</v>
       </c>
       <c r="D17" t="n">
-        <v>3.099400405752567</v>
+        <v>3.80650430287025</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
@@ -2641,17 +2641,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>current_phase_a_env_dom_rel_peak_power</t>
+          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.005814309490664997</v>
+        <v>0.005861206964102817</v>
       </c>
       <c r="C18" t="n">
-        <v>0.002392262923618838</v>
+        <v>0.001496784969615569</v>
       </c>
       <c r="D18" t="n">
-        <v>2.430454081246541</v>
+        <v>3.915838229739767</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
@@ -2665,17 +2665,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>current_phase_a_env_spread</t>
+          <t>current_phase_a_env_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.005609360693174905</v>
+        <v>0.005536521855461392</v>
       </c>
       <c r="C19" t="n">
-        <v>0.001040255975532233</v>
+        <v>0.001587374259622002</v>
       </c>
       <c r="D19" t="n">
-        <v>5.392237009679164</v>
+        <v>3.487827110481607</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
@@ -2689,17 +2689,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>current_phase_a_env_ptp</t>
+          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.005102004527475194</v>
+        <v>0.005397228992709968</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0009671044399762418</v>
+        <v>0.002388833358193196</v>
       </c>
       <c r="D20" t="n">
-        <v>5.275492037530253</v>
+        <v>2.259348221472406</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
@@ -2713,17 +2713,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
+          <t>current_phase_a_env_peak_power_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.004908871999660639</v>
+        <v>0.005243216504838167</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0008719829550210968</v>
+        <v>0.001776382039940231</v>
       </c>
       <c r="D21" t="n">
-        <v>5.629485847786321</v>
+        <v>2.951609997652648</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
@@ -2737,17 +2737,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_std</t>
+          <t>current_phase_a_env_peak_power_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.004514055030705375</v>
+        <v>0.004887488293802992</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0007688223826477266</v>
+        <v>0.0009290116359949035</v>
       </c>
       <c r="D22" t="n">
-        <v>5.871312307579638</v>
+        <v>5.260898244386855</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
@@ -2761,17 +2761,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
+          <t>current_phase_a_env_form_factor</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.004490512246723915</v>
+        <v>0.004882165656758908</v>
       </c>
       <c r="C23" t="n">
-        <v>0.001290593753912736</v>
+        <v>0.0006589783969020709</v>
       </c>
       <c r="D23" t="n">
-        <v>3.479388800094518</v>
+        <v>7.408576053402686</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
@@ -2785,17 +2785,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>current_phase_a_env_form_factor</t>
+          <t>current_phase_a_env_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.004192643141971529</v>
+        <v>0.00465627004655894</v>
       </c>
       <c r="C24" t="n">
-        <v>0.001207257572510422</v>
+        <v>0.001178641756892385</v>
       </c>
       <c r="D24" t="n">
-        <v>3.472836707817178</v>
+        <v>3.950505328932432</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
@@ -2809,17 +2809,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
+          <t>current_phase_a_current_phase_b_env_crest_diff</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.004032556107301291</v>
+        <v>0.004572613426248455</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00103163429914011</v>
+        <v>0.0008300466224263231</v>
       </c>
       <c r="D25" t="n">
-        <v>3.90886288099734</v>
+        <v>5.508796993730781</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
@@ -2833,17 +2833,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_mean</t>
+          <t>current_phase_a_form_factor</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.003875501892822657</v>
+        <v>0.004290043840928863</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0009110665951995959</v>
+        <v>0.001263021555436203</v>
       </c>
       <c r="D26" t="n">
-        <v>4.253760785034352</v>
+        <v>3.396624433066715</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
@@ -2857,17 +2857,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
+          <t>current_phase_a_env_peak_freq_cv</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.003739257071056482</v>
+        <v>0.004108003433930746</v>
       </c>
       <c r="C27" t="n">
-        <v>0.001322882167582336</v>
+        <v>0.001443861606666586</v>
       </c>
       <c r="D27" t="n">
-        <v>2.826577375456229</v>
+        <v>2.845130699269545</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.003685213311744041</v>
+        <v>0.003986213897685517</v>
       </c>
       <c r="C28" t="n">
-        <v>0.001507479369711071</v>
+        <v>0.00122911259463932</v>
       </c>
       <c r="D28" t="n">
-        <v>2.444603183139101</v>
+        <v>3.243137759464306</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
@@ -2905,17 +2905,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_freq_cv</t>
+          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.003638175386638028</v>
+        <v>0.003238483153555316</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0006481877397042869</v>
+        <v>0.0009902334474559988</v>
       </c>
       <c r="D29" t="n">
-        <v>5.612755435243871</v>
+        <v>3.270390894153548</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
@@ -2929,17 +2929,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>current_phase_a_skewness</t>
+          <t>current_phase_a_env_peak_sp_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.003232177103848286</v>
+        <v>0.002976160900144605</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0003603671265419705</v>
+        <v>0.0006334289492323715</v>
       </c>
       <c r="D30" t="n">
-        <v>8.96887417595816</v>
+        <v>4.698417903968873</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
@@ -2953,17 +2953,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>current_phase_a_env_harmonic_ratio</t>
+          <t>current_phase_a_env_peak_sp_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002723248825967044</v>
+        <v>0.002388622488174647</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0002766705035296973</v>
+        <v>0.0007361382533732556</v>
       </c>
       <c r="D31" t="n">
-        <v>9.842575791303439</v>
+        <v>3.244757393947823</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
@@ -2981,13 +2981,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002191618875370106</v>
+        <v>0.001164308682606743</v>
       </c>
       <c r="C32" t="n">
-        <v>0.001241927327103031</v>
+        <v>0.0004459926082983537</v>
       </c>
       <c r="D32" t="n">
-        <v>1.764677514349554</v>
+        <v>2.610542317339718</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.08947038215280392</v>
+        <v>0.0892521967843936</v>
       </c>
       <c r="F2" t="n">
-        <v>0.005083358800201473</v>
+        <v>0.004008361957354538</v>
       </c>
       <c r="G2" t="n">
-        <v>17.60060811429969</v>
+        <v>22.26644576250819</v>
       </c>
     </row>
     <row r="3">
@@ -3118,13 +3118,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.0598043314413836</v>
+        <v>0.05349509833719766</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003965517981583669</v>
+        <v>0.003637456486392708</v>
       </c>
       <c r="G3" t="n">
-        <v>15.08105143101278</v>
+        <v>14.70669174199018</v>
       </c>
     </row>
     <row r="4">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_env_thd_power_frac</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.01934626971777358</v>
+        <v>0.02075476983887545</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005117110359299441</v>
+        <v>0.003388256910477684</v>
       </c>
       <c r="G4" t="n">
-        <v>3.780694679697192</v>
+        <v>6.125482551181132</v>
       </c>
     </row>
     <row r="5">
@@ -3168,17 +3168,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>current_phase_a_env_thd_power_frac</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.01785408286752348</v>
+        <v>0.01635894896459728</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002003337538673498</v>
+        <v>0.00338062203455636</v>
       </c>
       <c r="G5" t="n">
-        <v>8.912124592892868</v>
+        <v>4.839020868695063</v>
       </c>
     </row>
     <row r="6">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_env_fundamental_power_ratio</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.01737711080385931</v>
+        <v>0.01448599006623655</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003500129330335388</v>
+        <v>0.00342001771375219</v>
       </c>
       <c r="G6" t="n">
-        <v>4.964691163364121</v>
+        <v>4.235635286809897</v>
       </c>
     </row>
     <row r="7">
@@ -3222,17 +3222,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.01119049018831471</v>
+        <v>0.01435504162927167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001634222966783054</v>
+        <v>0.002683987220386127</v>
       </c>
       <c r="G7" t="n">
-        <v>6.847548920973551</v>
+        <v>5.348381704809112</v>
       </c>
     </row>
     <row r="8">
@@ -3249,17 +3249,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>current_phase_a_env_ptp</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.009996664125381945</v>
+        <v>0.01321828918069374</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001506893360535688</v>
+        <v>0.002954038874866728</v>
       </c>
       <c r="G8" t="n">
-        <v>6.633911893214066</v>
+        <v>4.474634557727176</v>
       </c>
     </row>
     <row r="9">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>current_phase_a_env_fundamental_power_ratio</t>
+          <t>current_phase_a_kurtosis</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.009145379591010005</v>
+        <v>0.01273307814445003</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001887251195291373</v>
+        <v>0.001325689235362773</v>
       </c>
       <c r="G9" t="n">
-        <v>4.845847312405561</v>
+        <v>9.604801605671637</v>
       </c>
     </row>
     <row r="10">
@@ -3303,17 +3303,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_env_peak_freq_cv</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.008630382388641101</v>
+        <v>0.009375271019915376</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002914212626336436</v>
+        <v>0.002285166053528553</v>
       </c>
       <c r="G10" t="n">
-        <v>2.961469830975349</v>
+        <v>4.102647148537622</v>
       </c>
     </row>
     <row r="11">
@@ -3330,17 +3330,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>current_phase_a_env_skew</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.008334877817544778</v>
+        <v>0.008527769695530976</v>
       </c>
       <c r="F11" t="n">
-        <v>0.001769702756283999</v>
+        <v>0.00346929531284653</v>
       </c>
       <c r="G11" t="n">
-        <v>4.709734835751626</v>
+        <v>2.458062616730041</v>
       </c>
     </row>
     <row r="12">
@@ -3357,17 +3357,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_mean</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.007157449673629128</v>
+        <v>0.007979525085010387</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00208556742788595</v>
+        <v>0.0009550418300052336</v>
       </c>
       <c r="G12" t="n">
-        <v>3.43187914192392</v>
+        <v>8.355070200710111</v>
       </c>
     </row>
     <row r="13">
@@ -3384,17 +3384,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_skewness</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.007104264198398573</v>
+        <v>0.007849237663050197</v>
       </c>
       <c r="F13" t="n">
-        <v>0.002194874394543194</v>
+        <v>0.00141470211112165</v>
       </c>
       <c r="G13" t="n">
-        <v>3.236737304279361</v>
+        <v>5.548293254397145</v>
       </c>
     </row>
     <row r="14">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_env_peak_power_std</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.006354681821574208</v>
+        <v>0.007691985392600087</v>
       </c>
       <c r="F14" t="n">
-        <v>0.001253286656350524</v>
+        <v>0.00182410936543081</v>
       </c>
       <c r="G14" t="n">
-        <v>5.070373234760245</v>
+        <v>4.216821299292242</v>
       </c>
     </row>
     <row r="15">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_time_corr</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.006336957435771789</v>
+        <v>0.007075366517356023</v>
       </c>
       <c r="F15" t="n">
-        <v>0.001193097037751115</v>
+        <v>0.001335475946214278</v>
       </c>
       <c r="G15" t="n">
-        <v>5.311306727111681</v>
+        <v>5.297971526703571</v>
       </c>
     </row>
     <row r="16">
@@ -3465,17 +3465,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>current_phase_a_env_form_factor</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.006115930160840832</v>
+        <v>0.006926927307726595</v>
       </c>
       <c r="F16" t="n">
-        <v>0.001938746113071593</v>
+        <v>0.002256605423040095</v>
       </c>
       <c r="G16" t="n">
-        <v>3.154563959646939</v>
+        <v>3.069609131003232</v>
       </c>
     </row>
     <row r="17">
@@ -3496,13 +3496,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.1335743092130243</v>
+        <v>0.1207519052953107</v>
       </c>
       <c r="F17" t="n">
-        <v>0.01247936018049603</v>
+        <v>0.008861447449861266</v>
       </c>
       <c r="G17" t="n">
-        <v>10.70360982013237</v>
+        <v>13.62664166459449</v>
       </c>
     </row>
     <row r="18">
@@ -3523,13 +3523,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.06996646778779707</v>
+        <v>0.06981254261203576</v>
       </c>
       <c r="F18" t="n">
-        <v>0.009905552146559001</v>
+        <v>0.004737963465589383</v>
       </c>
       <c r="G18" t="n">
-        <v>7.063351554671943</v>
+        <v>14.7346841680447</v>
       </c>
     </row>
     <row r="19">
@@ -3550,13 +3550,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.02742571917860786</v>
+        <v>0.03380165670763714</v>
       </c>
       <c r="F19" t="n">
-        <v>0.001494243597575974</v>
+        <v>0.004368471176364656</v>
       </c>
       <c r="G19" t="n">
-        <v>18.35412624945239</v>
+        <v>7.737622148979033</v>
       </c>
     </row>
     <row r="20">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01905605451338522</v>
+        <v>0.01445695187077699</v>
       </c>
       <c r="F20" t="n">
-        <v>0.004208444717546862</v>
+        <v>0.001491310756378274</v>
       </c>
       <c r="G20" t="n">
-        <v>4.528040763735039</v>
+        <v>9.694059315506491</v>
       </c>
     </row>
     <row r="21">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.01723419891648958</v>
+        <v>0.01363966043589387</v>
       </c>
       <c r="F21" t="n">
-        <v>0.004297733926195545</v>
+        <v>0.003691638748959012</v>
       </c>
       <c r="G21" t="n">
-        <v>4.010057186386547</v>
+        <v>3.694734077758629</v>
       </c>
     </row>
     <row r="22">
@@ -3627,17 +3627,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.01181756374615098</v>
+        <v>0.01351857518865348</v>
       </c>
       <c r="F22" t="n">
-        <v>0.001615055837217617</v>
+        <v>0.003142131357462593</v>
       </c>
       <c r="G22" t="n">
-        <v>7.317078643995035</v>
+        <v>4.302344691319133</v>
       </c>
     </row>
     <row r="23">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>current_phase_a_env_entropy</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.01038047325630957</v>
+        <v>0.01007516981552319</v>
       </c>
       <c r="F23" t="n">
-        <v>0.001356663559808088</v>
+        <v>0.00158876742748563</v>
       </c>
       <c r="G23" t="n">
-        <v>7.651415612299518</v>
+        <v>6.34146082467194</v>
       </c>
     </row>
     <row r="24">
@@ -3681,17 +3681,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.01025048204327239</v>
+        <v>0.009830499748656915</v>
       </c>
       <c r="F24" t="n">
-        <v>0.004989974677409688</v>
+        <v>0.003228291489443207</v>
       </c>
       <c r="G24" t="n">
-        <v>2.054211126073726</v>
+        <v>3.045099654045139</v>
       </c>
     </row>
     <row r="25">
@@ -3708,17 +3708,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.009899670235698496</v>
+        <v>0.008654555308650997</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003113364655548736</v>
+        <v>0.001171974388591395</v>
       </c>
       <c r="G25" t="n">
-        <v>3.179723396943266</v>
+        <v>7.384531221489123</v>
       </c>
     </row>
     <row r="26">
@@ -3735,17 +3735,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_time_corr</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.008927770993022669</v>
+        <v>0.008648389374738821</v>
       </c>
       <c r="F26" t="n">
-        <v>0.002699311693834165</v>
+        <v>0.001809274329392492</v>
       </c>
       <c r="G26" t="n">
-        <v>3.307412752402069</v>
+        <v>4.780005681938731</v>
       </c>
     </row>
     <row r="27">
@@ -3762,17 +3762,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.008153133469123514</v>
+        <v>0.008391780740224305</v>
       </c>
       <c r="F27" t="n">
-        <v>0.001764201659899393</v>
+        <v>0.001367115219078149</v>
       </c>
       <c r="G27" t="n">
-        <v>4.621403233208684</v>
+        <v>6.138267821496901</v>
       </c>
     </row>
     <row r="28">
@@ -3789,17 +3789,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>current_phase_a_env_ptp</t>
+          <t>current_phase_a_env_flatness</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.007950204655173557</v>
+        <v>0.007240867880473423</v>
       </c>
       <c r="F28" t="n">
-        <v>0.001790489010741917</v>
+        <v>0.002733114074963257</v>
       </c>
       <c r="G28" t="n">
-        <v>4.440217284386706</v>
+        <v>2.649300830065963</v>
       </c>
     </row>
     <row r="29">
@@ -3816,17 +3816,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>current_phase_a_form_factor</t>
+          <t>current_phase_a_env_peak_freq_cv</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.007393227244433415</v>
+        <v>0.006773754587149681</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001440763860301628</v>
+        <v>0.001698681115792832</v>
       </c>
       <c r="G29" t="n">
-        <v>5.131427941707406</v>
+        <v>3.987631726671013</v>
       </c>
     </row>
     <row r="30">
@@ -3843,17 +3843,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>current_phase_a_env_spread</t>
+          <t>current_phase_a_env_peak_power_std</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.007164237881727155</v>
+        <v>0.006479958665383178</v>
       </c>
       <c r="F30" t="n">
-        <v>0.001554979350547505</v>
+        <v>0.001781201048950779</v>
       </c>
       <c r="G30" t="n">
-        <v>4.607258486500024</v>
+        <v>3.637951083449765</v>
       </c>
     </row>
     <row r="31">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_env_rms</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.007062869558926904</v>
+        <v>0.006265130908933175</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00108344121025426</v>
+        <v>0.002832124800902284</v>
       </c>
       <c r="G31" t="n">
-        <v>6.518862586594389</v>
+        <v>2.212158442083046</v>
       </c>
     </row>
     <row r="32">
@@ -3897,17 +3897,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_correlation</t>
+          <t>current_phase_a_rms</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.09205584583735392</v>
+        <v>0.0823856130692415</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01401714263324221</v>
+        <v>0.002177867569437301</v>
       </c>
       <c r="G32" t="n">
-        <v>6.567371294726433</v>
+        <v>37.8283950509337</v>
       </c>
     </row>
     <row r="33">
@@ -3924,17 +3924,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>current_phase_a_rms</t>
+          <t>current_phase_a_current_phase_b_correlation</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.0810782023322784</v>
+        <v>0.07999199579479901</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0131565216606536</v>
+        <v>0.004066370358822997</v>
       </c>
       <c r="G33" t="n">
-        <v>6.162581782458199</v>
+        <v>19.67154784751923</v>
       </c>
     </row>
     <row r="34">
@@ -3955,13 +3955,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.01238945955074899</v>
+        <v>0.01744738626763532</v>
       </c>
       <c r="F34" t="n">
-        <v>0.001903219293073832</v>
+        <v>0.003486317541083496</v>
       </c>
       <c r="G34" t="n">
-        <v>6.509704109660509</v>
+        <v>5.004517235409541</v>
       </c>
     </row>
     <row r="35">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.01226762620732598</v>
+        <v>0.01415767507146678</v>
       </c>
       <c r="F35" t="n">
-        <v>0.002776827850427346</v>
+        <v>0.003809326789379116</v>
       </c>
       <c r="G35" t="n">
-        <v>4.417840316256865</v>
+        <v>3.716572163149254</v>
       </c>
     </row>
     <row r="36">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>current_phase_a_env_fundamental_power_ratio</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.01213723371225801</v>
+        <v>0.01256166296600987</v>
       </c>
       <c r="F36" t="n">
-        <v>0.002129655634859482</v>
+        <v>0.001385053918971009</v>
       </c>
       <c r="G36" t="n">
-        <v>5.699126432614311</v>
+        <v>9.069374195627141</v>
       </c>
     </row>
     <row r="37">
@@ -4032,17 +4032,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_kurtosis</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.01178506510693582</v>
+        <v>0.01107588820576635</v>
       </c>
       <c r="F37" t="n">
-        <v>0.005153776826509512</v>
+        <v>0.0008682377329730983</v>
       </c>
       <c r="G37" t="n">
-        <v>2.286680746343064</v>
+        <v>12.75659905018091</v>
       </c>
     </row>
     <row r="38">
@@ -4059,17 +4059,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_env_fundamental_power_ratio</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.01099190334441814</v>
+        <v>0.009635984059141432</v>
       </c>
       <c r="F38" t="n">
-        <v>0.002738007829832694</v>
+        <v>0.001755795758989793</v>
       </c>
       <c r="G38" t="n">
-        <v>4.014547759570212</v>
+        <v>5.4880695144123</v>
       </c>
     </row>
     <row r="39">
@@ -4086,17 +4086,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>current_phase_a_env_skew</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.01090063583621146</v>
+        <v>0.009099656029478631</v>
       </c>
       <c r="F39" t="n">
-        <v>0.002252791901997871</v>
+        <v>0.002147713850842523</v>
       </c>
       <c r="G39" t="n">
-        <v>4.838701452863814</v>
+        <v>4.236883631901261</v>
       </c>
     </row>
     <row r="40">
@@ -4113,17 +4113,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_std</t>
+          <t>current_phase_a_env_spread</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.009925056130816201</v>
+        <v>0.008862603389878239</v>
       </c>
       <c r="F40" t="n">
-        <v>0.004659485924508484</v>
+        <v>0.00307378307514011</v>
       </c>
       <c r="G40" t="n">
-        <v>2.130070782680889</v>
+        <v>2.883279119065054</v>
       </c>
     </row>
     <row r="41">
@@ -4140,17 +4140,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>current_phase_a_form_factor</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.007829784030783892</v>
+        <v>0.008622907730825621</v>
       </c>
       <c r="F41" t="n">
-        <v>0.002193239529859956</v>
+        <v>0.001967799383131168</v>
       </c>
       <c r="G41" t="n">
-        <v>3.569946749872934</v>
+        <v>4.381983237169494</v>
       </c>
     </row>
     <row r="42">
@@ -4167,17 +4167,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_env_flatness</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.007469038311777962</v>
+        <v>0.007577123906339136</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0007629565975446013</v>
+        <v>0.001848535095065135</v>
       </c>
       <c r="G42" t="n">
-        <v>9.789469599082073</v>
+        <v>4.098966222986381</v>
       </c>
     </row>
     <row r="43">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_skewness</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.007355772010820912</v>
+        <v>0.00714738720381055</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0007189339418575967</v>
+        <v>0.002279230472864301</v>
       </c>
       <c r="G43" t="n">
-        <v>10.23135683126445</v>
+        <v>3.135863586534374</v>
       </c>
     </row>
     <row r="44">
@@ -4221,17 +4221,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.007232456798526332</v>
+        <v>0.007123055482060048</v>
       </c>
       <c r="F44" t="n">
-        <v>0.001457615645914035</v>
+        <v>0.0003969225598876777</v>
       </c>
       <c r="G44" t="n">
-        <v>4.961806770346076</v>
+        <v>17.94525368257948</v>
       </c>
     </row>
     <row r="45">
@@ -4248,17 +4248,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>current_phase_a_env_entropy</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.006878410690493131</v>
+        <v>0.006588009437970535</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0006362741681382009</v>
+        <v>0.001315459924734431</v>
       </c>
       <c r="G45" t="n">
-        <v>10.81028105825688</v>
+        <v>5.008103426842336</v>
       </c>
     </row>
     <row r="46">
@@ -4275,17 +4275,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_mean</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.00687048318827094</v>
+        <v>0.006350653751881742</v>
       </c>
       <c r="F46" t="n">
-        <v>0.002559438634194517</v>
+        <v>0.001425536768906066</v>
       </c>
       <c r="G46" t="n">
-        <v>2.684360645679903</v>
+        <v>4.454889794149019</v>
       </c>
     </row>
   </sheetData>
@@ -4342,801 +4342,801 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
+          <t>current_phase_a_env_peak_sp_mean</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004710187716018539</v>
+        <v>0.004431840687220879</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00394632276328411</v>
+        <v>0.003492102502151986</v>
       </c>
       <c r="F2" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G2" t="n">
-        <v>0.003739257071056482</v>
+        <v>0.002976160900144605</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_time_corr</t>
+          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006336957435771789</v>
+        <v>0.003753430244055544</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008927770993022669</v>
+        <v>0.003663689361454731</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.006267273554009012</v>
+        <v>0.003238483153555316</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
+          <t>current_phase_a_kurtosis</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00409939927326536</v>
+        <v>0.01273307814445003</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003497057621920722</v>
+        <v>0.006123552815314355</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003685213311744041</v>
+        <v>0.01107588820576635</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>current_phase_a_rms</t>
+          <t>current_phase_a_env_peak_power_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08947038215280392</v>
+        <v>0.005530457793740922</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1335743092130243</v>
+        <v>0.003596454229129025</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0810782023322784</v>
+        <v>0.005243216504838167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.008630382388641101</v>
+        <v>0.01435504162927167</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01025048204327239</v>
+        <v>0.01351857518865348</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007355772010820912</v>
+        <v>0.007123055482060048</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_env_form_factor</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01737711080385931</v>
+        <v>0.005471134990224325</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01905605451338522</v>
+        <v>0.004561172933485074</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007469038311777962</v>
+        <v>0.004882165656758908</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>current_phase_a_env_fundamental_power_ratio</t>
+          <t>current_phase_a_current_phase_b_env_crest_diff</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009145379591010005</v>
+        <v>0.00415584943348344</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01723419891648958</v>
+        <v>0.003007787692226889</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01213723371225801</v>
+        <v>0.004572613426248455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>current_phase_a_skewness</t>
+          <t>current_phase_a_env_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>0.004834556544988275</v>
+        <v>0.005063336554196192</v>
       </c>
       <c r="D9" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003451071616451398</v>
+        <v>0.006265130908933175</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003232177103848286</v>
+        <v>0.005536521855461392</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_correlation</t>
+          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0598043314413836</v>
+        <v>0.005273866514846195</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="E10" t="n">
-        <v>0.06996646778779707</v>
+        <v>0.003083919279418024</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
-        <v>0.09205584583735392</v>
+        <v>0.005861206964102817</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>current_phase_a_env_form_factor</t>
+          <t>current_phase_a_env_peak_freq_cv</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>0.006115930160840832</v>
+        <v>0.009375271019915376</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004290261043976759</v>
+        <v>0.006773754587149681</v>
       </c>
       <c r="F11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>0.004192643141971529</v>
+        <v>0.004108003433930746</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_mean</t>
+          <t>current_phase_a_env_thd_power_frac</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00424774008812694</v>
+        <v>0.02075476983887545</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002631362765628965</v>
+        <v>0.03380165670763714</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.003875501892822657</v>
+        <v>0.01744738626763532</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>current_phase_a_env_dom_rel_peak_power</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>0.005251352450626504</v>
+        <v>0.007979525085010387</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003761132378917233</v>
+        <v>0.008654555308650997</v>
       </c>
       <c r="F13" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.005814309490664997</v>
+        <v>0.01256166296600987</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>0.004348276181978208</v>
+        <v>0.01321828918069374</v>
       </c>
       <c r="D14" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.003753681503967562</v>
+        <v>0.01445695187077699</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.004490512246723915</v>
+        <v>0.009099656029478631</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_std</t>
+          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>0.004542299226515254</v>
+        <v>0.006350715936944357</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E15" t="n">
-        <v>0.002624069130280448</v>
+        <v>0.003790679890657642</v>
       </c>
       <c r="F15" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G15" t="n">
-        <v>0.004514055030705375</v>
+        <v>0.006025920240197833</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>current_phase_a_env_harmonic_count</t>
+          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>0.002222427240167349</v>
+        <v>0.005546382027397544</v>
       </c>
       <c r="D16" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001518027185887725</v>
+        <v>0.004308614990325007</v>
       </c>
       <c r="F16" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002191618875370106</v>
+        <v>0.003986213897685517</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_std</t>
+          <t>current_phase_a_env_flatness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>0.006048303256463411</v>
+        <v>0.004808392246997235</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>0.006458056982135013</v>
+        <v>0.007240867880473423</v>
       </c>
       <c r="F17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" t="n">
-        <v>0.009925056130816201</v>
+        <v>0.007577123906339136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_env_peak_sp_std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C18" t="n">
-        <v>0.007104264198398573</v>
+        <v>0.00308145843795001</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="E18" t="n">
-        <v>0.008153133469123514</v>
+        <v>0.00234930270648911</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01178506510693582</v>
+        <v>0.002388622488174647</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>current_phase_a_env_spread</t>
+          <t>current_phase_a_form_factor</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>0.005362686608860113</v>
+        <v>0.005393046706631337</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E19" t="n">
-        <v>0.007164237881727155</v>
+        <v>0.005405674279797802</v>
       </c>
       <c r="F19" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G19" t="n">
-        <v>0.005609360693174905</v>
+        <v>0.004290043840928863</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
+          <t>current_phase_a_env_spread</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>0.005059569858465314</v>
+        <v>0.00596851045469447</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>0.005195182895393068</v>
+        <v>0.004460549161624454</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004032556107301291</v>
+        <v>0.008862603389878239</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>current_phase_a_env_skew</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.01635894896459728</v>
+      </c>
+      <c r="D21" t="n">
         <v>10</v>
       </c>
-      <c r="C21" t="n">
-        <v>0.008334877817544778</v>
-      </c>
-      <c r="D21" t="n">
-        <v>16</v>
-      </c>
       <c r="E21" t="n">
-        <v>0.006683225039643095</v>
+        <v>0.008648389374738821</v>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01090063583621146</v>
+        <v>0.008622907730825621</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_mean</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007157449673629128</v>
+        <v>0.007075366517356023</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0.003110465896265891</v>
+        <v>0.01007516981552319</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G22" t="n">
-        <v>0.00687048318827094</v>
+        <v>0.006588009437970535</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.006354681821574208</v>
+        <v>0.004360354051122903</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E23" t="n">
-        <v>0.007062869558926904</v>
+        <v>0.004357253284877782</v>
       </c>
       <c r="F23" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="G23" t="n">
-        <v>0.01099190334441814</v>
+        <v>0.005397228992709968</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>current_phase_a_env_entropy</t>
+          <t>current_phase_a_env_ptp</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00589560173599492</v>
+        <v>0.004085609314207334</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>0.01038047325630957</v>
+        <v>0.004871891433446982</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>0.006878410690493131</v>
+        <v>0.00465627004655894</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>current_phase_a_env_harmonic_ratio</t>
+          <t>current_phase_a_env_fundamental_power_ratio</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
-        <v>0.003390196541462896</v>
+        <v>0.01448599006623655</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.002365517306634709</v>
+        <v>0.01363966043589387</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="G25" t="n">
-        <v>0.002723248825967044</v>
+        <v>0.009635984059141432</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>current_phase_a_env_thd_power_frac</t>
+          <t>frequency_hz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
-        <v>0.01785408286752348</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02742571917860786</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01238945955074899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01934626971777358</v>
+        <v>0.008527769695530976</v>
       </c>
       <c r="D27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E27" t="n">
-        <v>0.009899670235698496</v>
+        <v>0.008391780740224305</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>0.01226762620732598</v>
+        <v>0.006350653751881742</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>frequency_hz</t>
+          <t>current_phase_a_env_peak_power_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.007691985392600087</v>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.006479958665383178</v>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>0.004887488293802992</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>current_phase_a_env_ptp</t>
+          <t>current_phase_a_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>0.009996664125381945</v>
+        <v>0.007849237663050197</v>
       </c>
       <c r="D29" t="n">
+        <v>23</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.00402448561736194</v>
+      </c>
+      <c r="F29" t="n">
         <v>12</v>
       </c>
-      <c r="E29" t="n">
-        <v>0.007950204655173557</v>
-      </c>
-      <c r="F29" t="n">
-        <v>19</v>
-      </c>
       <c r="G29" t="n">
-        <v>0.005102004527475194</v>
+        <v>0.00714738720381055</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>0.003881633591173469</v>
+        <v>0.006926927307726595</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.00349516563862998</v>
+        <v>0.009830499748656915</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.004908871999660639</v>
+        <v>0.01415767507146678</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_env_harmonic_count</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C31" t="n">
-        <v>0.01119049018831471</v>
+        <v>0.00151080994582323</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01181756374615098</v>
+        <v>0.0009390473821616043</v>
       </c>
       <c r="F31" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G31" t="n">
-        <v>0.007232456798526332</v>
+        <v>0.001164308682606743</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_freq_cv</t>
+          <t>current_phase_a_current_phase_b_correlation</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>0.004638591599508209</v>
+        <v>0.05349509833719766</v>
       </c>
       <c r="D32" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>0.003743044993270597</v>
+        <v>0.06981254261203576</v>
       </c>
       <c r="F32" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003638175386638028</v>
+        <v>0.07999199579479901</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>current_phase_a_form_factor</t>
+          <t>current_phase_a_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.005445830249082585</v>
+        <v>0.0892521967843936</v>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.007393227244433415</v>
+        <v>0.1207519052953107</v>
       </c>
       <c r="F33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.007829784030783892</v>
+        <v>0.0823856130692415</v>
       </c>
     </row>
   </sheetData>
@@ -5219,7 +5219,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-11-04 17:54:52</t>
+          <t>2025-11-06 19:20:04</t>
         </is>
       </c>
     </row>
